--- a/data/trans_orig/P36BPD01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023</t>
+          <t>Población según si utilizan como principal grasa para cocinar el aceite de oliva en 2023 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335752</t>
+          <t>335222</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>377780</t>
+          <t>377756</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>275661</t>
+          <t>276794</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301404</t>
+          <t>301078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>625967</t>
+          <t>623631</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>673129</t>
+          <t>672753</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,69%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56852</t>
+          <t>57382</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34791</t>
+          <t>33658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29927</t>
+          <t>30303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77089</t>
+          <t>79425</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>387346</t>
+          <t>388234</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>412919</t>
+          <t>413522</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>473528</t>
+          <t>473826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>495845</t>
+          <t>496207</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>869650</t>
+          <t>870520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>904886</t>
+          <t>903163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10628</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36201</t>
+          <t>35313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>13039</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27908</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63144</t>
+          <t>62274</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>483362</t>
+          <t>482564</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>507242</t>
+          <t>507915</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>498582</t>
+          <t>498637</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>518109</t>
+          <t>516950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>989934</t>
+          <t>991424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1020313</t>
+          <t>1020352</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26189</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50069</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>25518</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43886</t>
+          <t>43831</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55585</t>
+          <t>55546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85964</t>
+          <t>84474</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,85%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>829889</t>
+          <t>829418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>871238</t>
+          <t>872767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>669253</t>
+          <t>668955</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>688723</t>
+          <t>688646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1508038</t>
+          <t>1508062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1556640</t>
+          <t>1557003</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13273</t>
+          <t>11744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>54622</t>
+          <t>55093</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>23164</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>42855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>39318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>88259</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>526691</t>
+          <t>525718</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>544563</t>
+          <t>544489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>516339</t>
+          <t>516218</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>531070</t>
+          <t>530110</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1047576</t>
+          <t>1047609</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1070483</t>
+          <t>1070305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13593</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>31026</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34917</t>
+          <t>35095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57824</t>
+          <t>57791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>349897</t>
+          <t>348873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>361001</t>
+          <t>361081</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>581755</t>
+          <t>581565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>602605</t>
+          <t>602262</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>936578</t>
+          <t>935972</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>962645</t>
+          <t>963044</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26803</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39955</t>
+          <t>40561</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>265689</t>
+          <t>266498</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276195</t>
+          <t>275797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>403657</t>
+          <t>403351</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>414784</t>
+          <t>414684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>674057</t>
+          <t>673706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>688899</t>
+          <t>689125</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15604</t>
+          <t>14795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>11147</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>22480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>18225</t>
+          <t>17999</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33067</t>
+          <t>33418</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3242677</t>
+          <t>3239663</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3318017</t>
+          <t>3314832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3468372</t>
+          <t>3467078</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3524900</t>
+          <t>3528030</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6728011</t>
+          <t>6725947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6820115</t>
+          <t>6823898</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,15%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>123690</t>
+          <t>126875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>199030</t>
+          <t>202044</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>130519</t>
+          <t>127389</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>187047</t>
+          <t>188341</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>277011</t>
+          <t>273228</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>369115</t>
+          <t>371179</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD01_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>361454</t>
+          <t>364972</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>335222</t>
+          <t>341344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>377756</t>
+          <t>381095</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>292073</t>
+          <t>331833</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>276794</t>
+          <t>314342</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>301078</t>
+          <t>344656</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>653527</t>
+          <t>696805</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>623631</t>
+          <t>669984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>672753</t>
+          <t>718496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>36284</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57382</t>
+          <t>59912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18379</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>14955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>45269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>64062</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30303</t>
+          <t>42371</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>90883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>392604</t>
+          <t>401256</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>392604</t>
+          <t>401256</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>392604</t>
+          <t>401256</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310452</t>
+          <t>359611</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>310452</t>
+          <t>359611</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310452</t>
+          <t>359611</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>703056</t>
+          <t>760867</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>703056</t>
+          <t>760867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>703056</t>
+          <t>760867</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>403236</t>
+          <t>444409</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>388234</t>
+          <t>427014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>413522</t>
+          <t>457133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>486477</t>
+          <t>462233</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>473826</t>
+          <t>447512</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>496207</t>
+          <t>473099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>889714</t>
+          <t>906642</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>870520</t>
+          <t>886809</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>903163</t>
+          <t>923268</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20311</t>
+          <t>32481</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>19757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35313</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13039</t>
+          <t>24811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35420</t>
+          <t>50398</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43080</t>
+          <t>68158</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>51532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62274</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>509246</t>
+          <t>497910</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>509246</t>
+          <t>497910</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>509246</t>
+          <t>497910</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>932794</t>
+          <t>974800</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>932794</t>
+          <t>974800</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>932794</t>
+          <t>974800</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>497249</t>
+          <t>563435</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>482564</t>
+          <t>545466</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>507915</t>
+          <t>577054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,22 +1446,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>509013</t>
+          <t>583281</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>498637</t>
+          <t>571847</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>516950</t>
+          <t>592983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1006261</t>
+          <t>1146717</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>991424</t>
+          <t>1125259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1020352</t>
+          <t>1163917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36182</t>
+          <t>54621</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>50867</t>
+          <t>72590</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>33455</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25518</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43831</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>69637</t>
+          <t>93479</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55546</t>
+          <t>76279</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84474</t>
+          <t>114937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>533431</t>
+          <t>618056</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>533431</t>
+          <t>618056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>533431</t>
+          <t>618056</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1075898</t>
+          <t>1240196</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1075898</t>
+          <t>1240196</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1075898</t>
+          <t>1240196</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>849462</t>
+          <t>654416</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>829418</t>
+          <t>639274</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>872767</t>
+          <t>665737</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>679620</t>
+          <t>697138</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>668955</t>
+          <t>686605</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>688646</t>
+          <t>705744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1529082</t>
+          <t>1351554</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1508062</t>
+          <t>1333978</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1557003</t>
+          <t>1366958</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>35049</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>31713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55093</t>
+          <t>58176</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32190</t>
+          <t>38599</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23164</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42855</t>
+          <t>49132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>67239</t>
+          <t>81633</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>66229</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88259</t>
+          <t>99209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>884511</t>
+          <t>697450</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>884511</t>
+          <t>697450</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>884511</t>
+          <t>697450</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711810</t>
+          <t>735737</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1596321</t>
+          <t>1433187</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1596321</t>
+          <t>1433187</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1596321</t>
+          <t>1433187</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>536694</t>
+          <t>581016</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>525718</t>
+          <t>569644</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>544489</t>
+          <t>589351</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>524250</t>
+          <t>582166</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>516218</t>
+          <t>573342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>530110</t>
+          <t>589021</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1060944</t>
+          <t>1163182</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1047609</t>
+          <t>1149395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1070305</t>
+          <t>1175044</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,76%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21462</t>
+          <t>25239</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13667</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32438</t>
+          <t>36611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22994</t>
+          <t>26014</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17134</t>
+          <t>19159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31026</t>
+          <t>34838</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>44456</t>
+          <t>51253</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35095</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57791</t>
+          <t>65040</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>558156</t>
+          <t>606255</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>558156</t>
+          <t>606255</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>558156</t>
+          <t>606255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547244</t>
+          <t>608180</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547244</t>
+          <t>608180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547244</t>
+          <t>608180</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1105400</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1105400</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1105400</t>
+          <t>1214435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>356187</t>
+          <t>392070</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>348873</t>
+          <t>384730</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>361081</t>
+          <t>397588</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>592402</t>
+          <t>421189</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>581565</t>
+          <t>414194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>602262</t>
+          <t>426210</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>948589</t>
+          <t>813259</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>935972</t>
+          <t>802485</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>963044</t>
+          <t>820987</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,02%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11978</t>
+          <t>15010</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>9492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>22350</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15966</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26803</t>
+          <t>24972</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27944</t>
+          <t>32987</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13489</t>
+          <t>25259</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40561</t>
+          <t>43761</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>272164</t>
+          <t>298298</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>266498</t>
+          <t>292066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>275797</t>
+          <t>302769</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>409918</t>
+          <t>446340</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>403351</t>
+          <t>439741</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>414684</t>
+          <t>451754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>682081</t>
+          <t>744638</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>673706</t>
+          <t>734189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>689125</t>
+          <t>752051</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,28%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14795</t>
+          <t>16434</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>18269</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11147</t>
+          <t>12855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22480</t>
+          <t>24868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>25043</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>17999</t>
+          <t>21058</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33418</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281293</t>
+          <t>308500</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>281293</t>
+          <t>308500</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>281293</t>
+          <t>308500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>707124</t>
+          <t>773109</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>707124</t>
+          <t>773109</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>707124</t>
+          <t>773109</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>3276446</t>
+          <t>3298616</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3239663</t>
+          <t>3260980</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3314832</t>
+          <t>3328952</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3493752</t>
+          <t>3524181</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3467078</t>
+          <t>3495998</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3528030</t>
+          <t>3551130</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6770198</t>
+          <t>6822797</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6725947</t>
+          <t>6771769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6823898</t>
+          <t>6861831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>165261</t>
+          <t>216872</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>126875</t>
+          <t>186536</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202044</t>
+          <t>254508</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>161667</t>
+          <t>203171</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127389</t>
+          <t>176222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>231354</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>326928</t>
+          <t>420043</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>273228</t>
+          <t>381009</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371179</t>
+          <t>471071</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3441707</t>
+          <t>3515488</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3655419</t>
+          <t>3727352</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7097126</t>
+          <t>7242840</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
